--- a/FTM Score Weights 2026.xlsx
+++ b/FTM Score Weights 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://michiganstate-my.sharepoint.com/personal/tianjiah_msu_edu/Documents/Data Manager/followup_dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{CF541428-8520-40CB-95F4-A7221B036C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{20275C4D-4ED0-364B-80B8-1E3FCD120BB3}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{CF541428-8520-40CB-95F4-A7221B036C63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1D5D8492-BCCD-094A-9B5E-87346AED50F6}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{E7A1A669-C0F1-41FB-94C3-6238C033C2EE}"/>
+    <workbookView xWindow="-4620" yWindow="-21000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{E7A1A669-C0F1-41FB-94C3-6238C033C2EE}"/>
   </bookViews>
   <sheets>
     <sheet name="12mo-20yr Call List " sheetId="2" r:id="rId1"/>
@@ -577,7 +577,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -608,6 +608,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -615,6 +621,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -626,22 +641,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -817,6 +816,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1163,19 +1166,19 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="A2" s="19" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
+      <c r="A3" s="19"/>
       <c r="B3" t="s">
         <v>14</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="24" t="s">
         <v>27</v>
       </c>
       <c r="E3" t="s">
@@ -1183,20 +1186,20 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="D4" s="20"/>
+      <c r="D4" s="25"/>
       <c r="E4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="26" t="s">
         <v>25</v>
       </c>
       <c r="B5" s="2"/>
@@ -1205,14 +1208,14 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A6" s="19"/>
+      <c r="A6" s="24"/>
       <c r="B6" t="s">
         <v>14</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="24" t="s">
         <v>27</v>
       </c>
       <c r="E6" t="s">
@@ -1220,20 +1223,20 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="20"/>
+      <c r="A7" s="25"/>
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="1">
         <v>1</v>
       </c>
-      <c r="D7" s="20"/>
+      <c r="D7" s="25"/>
       <c r="E7" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="18" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="2"/>
@@ -1242,14 +1245,14 @@
       <c r="E8" s="2"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A9" s="17"/>
+      <c r="A9" s="19"/>
       <c r="B9" t="s">
         <v>14</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E9" t="s">
@@ -1257,20 +1260,20 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="18"/>
+      <c r="A10" s="20"/>
       <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C10" s="1">
         <v>1</v>
       </c>
-      <c r="D10" s="18"/>
+      <c r="D10" s="20"/>
       <c r="E10" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="18" t="s">
         <v>18</v>
       </c>
       <c r="B11" s="2"/>
@@ -1279,14 +1282,14 @@
       <c r="E11" s="2"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A12" s="17"/>
+      <c r="A12" s="19"/>
       <c r="B12" t="s">
         <v>14</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
@@ -1294,33 +1297,33 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A13" s="17"/>
+      <c r="A13" s="19"/>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13">
         <v>1</v>
       </c>
-      <c r="D13" s="17"/>
+      <c r="D13" s="19"/>
       <c r="E13" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="65" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="18"/>
+      <c r="A14" s="20"/>
       <c r="B14" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="1">
         <v>1</v>
       </c>
-      <c r="D14" s="18"/>
+      <c r="D14" s="20"/>
       <c r="E14" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="18" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="2"/>
@@ -1329,14 +1332,14 @@
       <c r="E15" s="2"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A16" s="17"/>
+      <c r="A16" s="19"/>
       <c r="B16" t="s">
         <v>20</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="19" t="s">
         <v>24</v>
       </c>
       <c r="E16" t="s">
@@ -1344,14 +1347,14 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="17"/>
+      <c r="A17" s="19"/>
       <c r="B17" t="s">
         <v>21</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
-      <c r="D17" s="17"/>
+      <c r="D17" s="19"/>
       <c r="E17" t="s">
         <v>9</v>
       </c>
@@ -1382,7 +1385,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" customWidth="1"/>
-    <col min="2" max="2" width="8.83203125" style="27"/>
+    <col min="2" max="2" width="0" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
     <col min="6" max="6" width="35.6640625" customWidth="1"/>
   </cols>
@@ -1408,10 +1411,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="21">
         <v>2</v>
       </c>
       <c r="C2" s="7"/>
@@ -1420,15 +1423,15 @@
       <c r="F2" s="7"/>
     </row>
     <row r="3" spans="1:6" ht="48" x14ac:dyDescent="0.2">
-      <c r="A3" s="17"/>
-      <c r="B3" s="24"/>
+      <c r="A3" s="19"/>
+      <c r="B3" s="22"/>
       <c r="C3" t="s">
         <v>14</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="24" t="s">
         <v>31</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -1436,29 +1439,29 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A4" s="17"/>
-      <c r="B4" s="24"/>
+      <c r="A4" s="19"/>
+      <c r="B4" s="22"/>
       <c r="C4" t="s">
         <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="19"/>
+      <c r="E4" s="24"/>
       <c r="F4" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="25"/>
+      <c r="A5" s="20"/>
+      <c r="B5" s="23"/>
       <c r="C5" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D5" s="1">
         <v>0.25</v>
       </c>
-      <c r="E5" s="20"/>
+      <c r="E5" s="25"/>
       <c r="F5" s="1" t="s">
         <v>33</v>
       </c>
@@ -1474,7 +1477,7 @@
       <c r="D6" s="2">
         <v>0</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1490,7 +1493,7 @@
       <c r="D7" s="9">
         <v>1</v>
       </c>
-      <c r="E7" s="26"/>
+      <c r="E7" s="17"/>
       <c r="F7" s="9" t="s">
         <v>49</v>
       </c>
@@ -1506,7 +1509,7 @@
       <c r="D8" s="7">
         <v>0</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F8" t="s">
@@ -1522,7 +1525,7 @@
       <c r="D9" s="9">
         <v>1</v>
       </c>
-      <c r="E9" s="26"/>
+      <c r="E9" s="17"/>
       <c r="F9" s="9" t="s">
         <v>50</v>
       </c>
@@ -1538,7 +1541,7 @@
       <c r="D10" s="7">
         <v>0</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F10" t="s">
@@ -1554,7 +1557,7 @@
       <c r="D11" s="9">
         <v>1</v>
       </c>
-      <c r="E11" s="26"/>
+      <c r="E11" s="17"/>
       <c r="F11" s="9" t="s">
         <v>51</v>
       </c>
@@ -1570,7 +1573,7 @@
       <c r="D12" s="7">
         <v>0</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F12" t="s">
@@ -1586,7 +1589,7 @@
       <c r="D13" s="9">
         <v>1</v>
       </c>
-      <c r="E13" s="26"/>
+      <c r="E13" s="17"/>
       <c r="F13" s="9" t="s">
         <v>44</v>
       </c>
@@ -1602,7 +1605,7 @@
       <c r="D14" s="7">
         <v>0</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="2" t="s">
@@ -1618,7 +1621,7 @@
       <c r="D15" s="9">
         <v>1</v>
       </c>
-      <c r="E15" s="26"/>
+      <c r="E15" s="17"/>
       <c r="F15" s="9" t="s">
         <v>53</v>
       </c>
@@ -1634,7 +1637,7 @@
       <c r="D16" s="7">
         <v>0</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="7" t="s">
@@ -1650,7 +1653,7 @@
       <c r="D17" s="9">
         <v>1</v>
       </c>
-      <c r="E17" s="26"/>
+      <c r="E17" s="17"/>
       <c r="F17" s="9" t="s">
         <v>55</v>
       </c>
@@ -1666,7 +1669,7 @@
       <c r="D18" s="7">
         <v>0</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="7" t="s">
@@ -1682,7 +1685,7 @@
       <c r="D19" s="9">
         <v>1</v>
       </c>
-      <c r="E19" s="26"/>
+      <c r="E19" s="17"/>
       <c r="F19" s="9" t="s">
         <v>57</v>
       </c>
@@ -1698,7 +1701,7 @@
       <c r="D20" s="7">
         <v>0</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="7" t="s">
@@ -1714,7 +1717,7 @@
       <c r="D21" s="9">
         <v>1</v>
       </c>
-      <c r="E21" s="26"/>
+      <c r="E21" s="17"/>
       <c r="F21" s="9" t="s">
         <v>59</v>
       </c>
@@ -1730,7 +1733,7 @@
       <c r="D22" s="7">
         <v>0</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="7" t="s">
@@ -1746,7 +1749,7 @@
       <c r="D23" s="9">
         <v>1</v>
       </c>
-      <c r="E23" s="26"/>
+      <c r="E23" s="17"/>
       <c r="F23" s="9" t="s">
         <v>61</v>
       </c>
@@ -1762,7 +1765,7 @@
       <c r="D24" s="7">
         <v>0</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="16" t="s">
         <v>24</v>
       </c>
       <c r="F24" s="7" t="s">
@@ -1778,13 +1781,18 @@
       <c r="D25" s="9">
         <v>1</v>
       </c>
-      <c r="E25" s="26"/>
+      <c r="E25" s="17"/>
       <c r="F25" s="9" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="E3:E5"/>
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="E20:E21"/>
     <mergeCell ref="E22:E23"/>
     <mergeCell ref="E24:E25"/>
     <mergeCell ref="E6:E7"/>
@@ -1793,11 +1801,6 @@
     <mergeCell ref="E14:E15"/>
     <mergeCell ref="E16:E17"/>
     <mergeCell ref="E8:E9"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="E3:E5"/>
-    <mergeCell ref="E18:E19"/>
-    <mergeCell ref="E20:E21"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
